--- a/output/pdf_financials_xlsx/MRT.UN.xlsx
+++ b/output/pdf_financials_xlsx/MRT.UN.xlsx
@@ -2353,22 +2353,22 @@
         <v>14.752</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10.652</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.783</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>9.712</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>7.278</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.897</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>7.085</v>
       </c>
     </row>
     <row r="35">
@@ -2457,22 +2457,22 @@
         <v>14.752</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>10.652</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.783</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>9.712</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>7.278</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>7.897</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>7.085</v>
       </c>
     </row>
     <row r="37">
@@ -3081,22 +3081,22 @@
         <v>0.842</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>21.219</v>
+        <v>10.567</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.895</v>
+        <v>1.112</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>10.912</v>
+        <v>1.2</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>8.504</v>
+        <v>1.226</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>11.335</v>
+        <v>3.438</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>11.162</v>
+        <v>4.077</v>
       </c>
     </row>
     <row r="49">
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-4.927</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-43.885</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-18.106</v>
       </c>
     </row>
     <row r="125">
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-4.927</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -7137,13 +7137,13 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-43.885</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-18.106</v>
       </c>
     </row>
     <row r="126">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -29892,7 +29892,11 @@
           <t>Repayment of bank indebtedness 10</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33890,7 +33894,11 @@
           <t>Repayment of bank indebtedness 9</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -52849,7 +52857,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -55796,7 +55804,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -58759,7 +58767,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -60436,7 +60444,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -63717,7 +63725,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -68337,7 +68345,7 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -70586,7 +70594,7 @@
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
@@ -72127,7 +72135,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -74398,7 +74406,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
@@ -78155,7 +78163,7 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E788" s="5" t="n">

--- a/output/pdf_financials_xlsx/MRT.UN.xlsx
+++ b/output/pdf_financials_xlsx/MRT.UN.xlsx
@@ -1507,8 +1507,10 @@
       <c r="B20" s="3" t="n">
         <v>84.22199999999999</v>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>174.364</v>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>158.302</v>
@@ -1560,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>4.177</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1999,19 +2001,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>38.421</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -2029,19 +2031,19 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2051,19 +2053,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>84.22199999999999</v>
+        <v>122.643</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>174.364</v>
+        <v>174.443</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>158.302</v>
+        <v>158.35</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>228.446</v>
+        <v>228.489</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>212.381</v>
+        <v>212.419</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>113.882</v>
@@ -2081,19 +2083,19 @@
         <v>73.015</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>14.84</v>
+        <v>14.923</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-86.09699999999999</v>
+        <v>-86.014</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-74.44499999999999</v>
+        <v>-74.369</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-58.823</v>
+        <v>-58.745</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-16.561</v>
+        <v>-16.49</v>
       </c>
     </row>
     <row r="30">
@@ -4262,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="71">
@@ -4314,19 +4316,19 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="72">
@@ -4522,19 +4524,19 @@
         <v>307.291</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>306.319</v>
+        <v>306.196</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>408.853</v>
+        <v>408.686</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>458.115</v>
+        <v>458.027</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>358.972</v>
+        <v>358.811</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>589.217</v>
+        <v>589.045</v>
       </c>
     </row>
     <row r="76">
@@ -4804,19 +4806,19 @@
         </is>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.007150067513600283</v>
+        <v>0.007230069178675589</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.01559151450094592</v>
+        <v>0.0157504367984104</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.01695303193453914</v>
+        <v>0.01704458558966276</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.01857667770832603</v>
+        <v>0.01875875764933665</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.0187968142325675</v>
+        <v>0.01899572231968462</v>
       </c>
     </row>
     <row r="81">
@@ -9222,7 +9224,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -13419,7 +13425,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -53037,7 +53047,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -53089,19 +53103,19 @@
         </is>
       </c>
       <c r="O508" s="5" t="n">
-        <v>-0.083</v>
+        <v>0.083</v>
       </c>
       <c r="P508" s="5" t="n">
-        <v>-0.083</v>
+        <v>0.083</v>
       </c>
       <c r="Q508" s="5" t="n">
-        <v>-0.076</v>
+        <v>0.076</v>
       </c>
       <c r="R508" s="5" t="n">
-        <v>-0.078</v>
+        <v>0.078</v>
       </c>
       <c r="S508" s="5" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="509">
@@ -65857,7 +65871,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
@@ -68529,7 +68547,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
           <t>-</t>
@@ -74590,7 +74612,11 @@
           <t>Amortization expense 3, 5, 11 42,553</t>
         </is>
       </c>
-      <c r="D749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E749" t="inlineStr">
         <is>
           <t>-</t>
@@ -75320,7 +75346,11 @@
           <t>Income from discontinued operations 20 323</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr"/>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E757" t="inlineStr">
         <is>
           <t>-</t>
@@ -78349,7 +78379,11 @@
           <t>Amortization expense 3, 5, 12 37,058</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E790" s="5" t="n">
         <v>38.421</v>
       </c>
